--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260923.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,400,000</t>
+          <t>8,400,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.74%</t>
+          <t>13.73%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>7.49%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.28%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>5.25%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.67%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>4.04%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -836,24 +836,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,060,000</t>
+          <t>1,827,956</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,44 +865,44 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,867,956</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>120,500</t>
+          <t>840,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>840,000</t>
+          <t>95,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1100,29 +1100,29 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>680,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>470,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1210,24 +1210,24 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,198 +1261,198 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>191,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>191,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1469,90 +1469,90 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,121,787,272</t>
+          <t>7,570,449,088</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,628,895,497</t>
+          <t>6,063,140,450</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>3,992,237,825</t>
+          <t>3,962,409,492</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
